--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.84224587635053</v>
+        <v>12.16186495490696</v>
       </c>
       <c r="D2" t="n">
-        <v>14.90396877755582</v>
+        <v>2.421894926352822</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F2" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.11692323326409</v>
+        <v>10.25650002540542</v>
       </c>
       <c r="D3" t="n">
-        <v>26.31539473388153</v>
+        <v>4.276251644255749</v>
       </c>
       <c r="E3" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F3" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.76875370319082</v>
+        <v>9.549922476768508</v>
       </c>
       <c r="D4" t="n">
-        <v>16.42886668611921</v>
+        <v>2.669690836494373</v>
       </c>
       <c r="E4" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F4" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.05830436120765</v>
+        <v>7.646974458696244</v>
       </c>
       <c r="D5" t="n">
-        <v>3.781245556613382</v>
+        <v>0.6144524029496746</v>
       </c>
       <c r="E5" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F5" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.04584029349776</v>
+        <v>3.094949047693386</v>
       </c>
       <c r="D6" t="n">
-        <v>24.5686104214329</v>
+        <v>3.992399193482846</v>
       </c>
       <c r="E6" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F6" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.98962513584503</v>
+        <v>5.848314084574818</v>
       </c>
       <c r="D7" t="n">
-        <v>13.57122992005237</v>
+        <v>2.205324862008511</v>
       </c>
       <c r="E7" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F7" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.34126803930155</v>
+        <v>6.880456056386501</v>
       </c>
       <c r="D8" t="n">
-        <v>40.70027866274236</v>
+        <v>6.613795282695635</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F8" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.89019002229734</v>
+        <v>3.232155878623318</v>
       </c>
       <c r="D9" t="n">
-        <v>22.78771735404965</v>
+        <v>3.703004070033069</v>
       </c>
       <c r="E9" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F9" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.58312831584336</v>
+        <v>5.457258351324547</v>
       </c>
       <c r="D10" t="n">
-        <v>25.82902014710649</v>
+        <v>4.197215773904805</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F10" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.48500616405259</v>
+        <v>5.441313501658547</v>
       </c>
       <c r="D11" t="n">
-        <v>33.71663245819131</v>
+        <v>5.478952774456088</v>
       </c>
       <c r="E11" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F11" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.85251473479449</v>
+        <v>3.226033644404105</v>
       </c>
       <c r="D12" t="n">
-        <v>16.91082175784159</v>
+        <v>2.748008535649258</v>
       </c>
       <c r="E12" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F12" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.66062064252815</v>
+        <v>5.144850854410825</v>
       </c>
       <c r="D13" t="n">
-        <v>29.94932049238297</v>
+        <v>4.866764580012232</v>
       </c>
       <c r="E13" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F13" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.46072190815421</v>
+        <v>5.437367310075059</v>
       </c>
       <c r="D14" t="n">
-        <v>37.26578569163288</v>
+        <v>6.055690174890343</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F14" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>60.73720030212598</v>
+        <v>9.869795049095472</v>
       </c>
       <c r="D15" t="n">
-        <v>55.75651845808289</v>
+        <v>9.060434249438471</v>
       </c>
       <c r="E15" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F15" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.20707848845873</v>
+        <v>7.508650254374543</v>
       </c>
       <c r="D16" t="n">
-        <v>52.63137623504691</v>
+        <v>8.552598638195123</v>
       </c>
       <c r="E16" t="n">
-        <v>16.45021435337164</v>
+        <v>2.673159832422892</v>
       </c>
       <c r="F16" t="n">
-        <v>13.97323339855042</v>
+        <v>2.270650427264442</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
